--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8983,6 +8983,4311 @@
         <v>0</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>PV008448-PV008641, PV407014-PV407203,  PV419497-PV419583</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Cameroon, Cote d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2022-2024</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>40391923</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2017-2020</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2006-2024</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>RT, PR, IN</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2017-2021</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>RT,PR</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2011-2021</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>PV526713-PV526742</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2007-2022</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2021-2023</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>NRTI,NNRTI,PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>PX133190–PX134237</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2019-2022</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>RT, IN, NC, Env</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>1997-2019</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2015-2021</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>249 (uncertain)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>PI, INSTI, NRTI (presumably)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2022-2024</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>NRTI,NNRTI,INSTI</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Yes (some)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867)</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>41029850</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI, CAI</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2018-2023</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>NRTI,NNRTI,PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>PV187006</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr"/>
+      <c r="E510" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+      <c r="E511" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Yes (recombinant clones)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>PQ735970–PQ735985</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>PP280627- PP280757</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2017-2018</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>RT, PR, IN</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>RT,PR,IN,CA</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>NRTI, CAI</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+      <c r="E550" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E627"/>
+  <dimension ref="A1:E451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8952,17 +8952,15 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>227</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>PV008448-PV008641, PV407014-PV407203, PV419497-PV419583</t>
+          <t>488</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -8972,22 +8970,20 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>PV008448-PV008641, PV407014-PV407203,  PV419497-PV419583</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>47</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Integrase, PR, RT</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -8997,7 +8993,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9007,12 +9003,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -9022,22 +9018,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Cameroon, Cote d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>Hair</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -9047,22 +9043,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>Yes (PrEP)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -9072,22 +9068,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Plasma; DBS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -9097,22 +9093,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -9122,7 +9118,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9130,14 +9126,12 @@
           <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="C350" t="n">
+        <v>1</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -9147,22 +9141,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -9172,22 +9166,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2006-2024</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -9197,22 +9191,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>RT, PR, IN</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Tenofovir (TFV), Lamivudine (3TC), Darunavir (DRV)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -9222,22 +9216,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, RAL</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -9247,18 +9241,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT; Integrase, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -9268,22 +9266,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -9293,22 +9291,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2017-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -9318,22 +9316,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2017-2020</t>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -9343,22 +9341,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -9368,22 +9366,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -9393,22 +9391,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -9418,22 +9416,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -9443,22 +9441,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, PI, NNRTI</t>
+          <t>ATV/r, NFV, D4T, NVP, RAL</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -9468,7 +9466,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -9478,12 +9476,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>TDF/TAF, FTC/3TC, bictegravir, darunavir, dolutegravir, raltegravir, ABC, rilpivirine</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -9493,22 +9491,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -9518,22 +9516,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -9543,22 +9541,20 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>212</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -9568,22 +9564,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -9593,7 +9589,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -9603,12 +9599,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>RT, PR, IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -9618,22 +9614,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>Not reported</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -9643,22 +9639,20 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>0</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -9668,22 +9662,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -9693,18 +9687,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -9714,22 +9712,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -9739,22 +9737,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2017-2021</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -9764,22 +9762,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2017-2021</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -9789,22 +9787,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>RT,PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -9814,22 +9812,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -9839,22 +9837,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -9864,18 +9862,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -9885,18 +9887,20 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>0</v>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Protease, RT</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -9906,22 +9910,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>187</t>
+          <t xml:space="preserve">Yes  </t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -9931,22 +9935,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2011-2021</t>
+          <t>Envelope; Integrase; Near full length genome</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -9956,7 +9960,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -9966,12 +9970,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2011-2021</t>
+          <t>Sanger, NGS</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Illumina sequencing</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -9981,7 +9985,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -9991,12 +9995,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -10006,22 +10010,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -10031,22 +10035,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -10056,12 +10060,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10081,22 +10085,20 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>0</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -10106,22 +10108,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+          <t>Protease, PR; Gag</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -10131,22 +10133,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -10156,18 +10158,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr"/>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Envelope</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -10177,22 +10183,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -10202,22 +10208,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>INSTI, PI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -10227,22 +10233,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -10252,22 +10258,20 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>223</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Plasma; Serum</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -10277,22 +10281,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -10302,22 +10306,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC (Whole blood OK)</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -10327,18 +10331,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ATV/r, NFV, D4T, NVP, RAL</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -10348,22 +10356,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -10373,22 +10381,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -10398,22 +10406,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Whole genome</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Full genome</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -10423,22 +10431,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2007-2022</t>
+          <t>2015-2021</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -10448,22 +10456,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2007-2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -10473,22 +10481,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -10498,22 +10506,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -10523,22 +10531,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -10548,22 +10556,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -10573,22 +10581,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -10598,22 +10606,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -10623,22 +10631,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -10648,7 +10656,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -10656,10 +10664,14 @@
           <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -10669,22 +10681,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -10694,22 +10706,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -10719,22 +10731,20 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>10</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Illumina sequencing</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -10744,22 +10754,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -10769,22 +10779,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -10794,22 +10804,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -10819,7 +10829,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10829,12 +10839,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -10844,22 +10854,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -10869,7 +10879,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10879,12 +10889,12 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine (AZT), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Dolutegravir (DTG)</t>
+          <t>AZT, D4T, TDF, ABC</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -10894,18 +10904,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT; Integrase, IN; Protease, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -10915,22 +10929,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>Whole genome</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Near full length genome</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -10940,22 +10954,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -10965,22 +10979,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Sanger sequencing; Next-generation sequencing</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -10990,22 +11004,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Plasma; DBS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -11015,17 +11029,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11040,7 +11054,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11048,14 +11062,12 @@
           <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="C428" t="n">
+        <v>0</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -11065,22 +11077,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -11090,7 +11102,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -11100,12 +11112,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -11115,7 +11127,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11125,12 +11137,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
+          <t>Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -11140,18 +11152,22 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>No (Published sequences only)</t>
+        </is>
+      </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -11161,22 +11177,20 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>0</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>8654, 10551</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -11186,22 +11200,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Illumina sequencing</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -11211,22 +11225,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>1978-2023</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -11236,22 +11250,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -11261,22 +11275,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -11286,22 +11300,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -11311,22 +11325,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI, INSTI</t>
+          <t xml:space="preserve"> No</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -11336,18 +11350,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -11357,22 +11375,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -11382,22 +11400,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>PP280627- PP280757</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>PP280627 to PP280757</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -11407,22 +11425,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -11432,22 +11450,22 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -11457,22 +11475,20 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>64</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -11482,22 +11498,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (single genome)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -11507,22 +11523,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -11532,22 +11548,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -11557,22 +11573,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -11582,18 +11598,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -11603,4341 +11623,25 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E452" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E453" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E454" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="E455" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
-      <c r="E456" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>Bictegravir (BIC), Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir (TFV)</t>
-        </is>
-      </c>
-      <c r="E457" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E458" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E459" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>2004-2021</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E460" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E461" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E462" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>9685</t>
-        </is>
-      </c>
-      <c r="E463" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E464" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E465" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
-        </is>
-      </c>
-      <c r="E466" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>PX133190-PX134237</t>
-        </is>
-      </c>
-      <c r="E467" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>PX133190–PX134237</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
-        </is>
-      </c>
-      <c r="E468" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E469" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>2019-2022</t>
-        </is>
-      </c>
-      <c r="E470" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>2019-2022</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E471" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E472" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="E473" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E474" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INST</t>
-        </is>
-      </c>
-      <c r="E475" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E476" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E477" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>Envelope; Integrase; Near full length genome</t>
-        </is>
-      </c>
-      <c r="E478" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>Illumina sequencing</t>
-        </is>
-      </c>
-      <c r="E479" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E480" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
-      </c>
-      <c r="E481" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E482" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>INSTI</t>
-        </is>
-      </c>
-      <c r="E483" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Dolutegravir (DTG)</t>
-        </is>
-      </c>
-      <c r="E484" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E485" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Protease, PR; Gag</t>
-        </is>
-      </c>
-      <c r="E486" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E487" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E488" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E489" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E490" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>INSTI, PI, NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E491" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
-        </is>
-      </c>
-      <c r="E492" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
-        </is>
-      </c>
-      <c r="E493" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E494" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>1997-2019</t>
-        </is>
-      </c>
-      <c r="E495" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>1997-2019</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E496" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>Whole Blood</t>
-        </is>
-      </c>
-      <c r="E497" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>PBMC (Whole blood OK)</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E498" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="E499" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>INSTI, NRTI</t>
-        </is>
-      </c>
-      <c r="E500" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir alafenamide (TAF)</t>
-        </is>
-      </c>
-      <c r="E501" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>Full genome</t>
-        </is>
-      </c>
-      <c r="E502" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E503" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
-      <c r="E504" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>Illumina sequencing</t>
-        </is>
-      </c>
-      <c r="E505" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
-      <c r="E506" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="E507" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E508" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E509" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>Yes (Only past sequences)</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E510" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>249 (uncertain)</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E511" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E512" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>PR, RT, IN (presumably)</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E513" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="E514" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E515" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>DRV, DTG</t>
-        </is>
-      </c>
-      <c r="E516" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>Integrase, IN</t>
-        </is>
-      </c>
-      <c r="E517" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="E518" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>2022-2024</t>
-        </is>
-      </c>
-      <c r="E519" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>2022-2024</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E520" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>RT,IN</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E521" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E522" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E523" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E524" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E525" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>NRTI,NNRTI,INSTI</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E526" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>Yes (some)</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747, PQ893191</t>
-        </is>
-      </c>
-      <c r="E527" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867)</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
-        </is>
-      </c>
-      <c r="E528" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="E529" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="E530" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E531" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E532" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E533" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="E534" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E535" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E536" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>ABC, AZT, 3TC, DTG, NVP, EFV, ATV, DRV, LPV</t>
-        </is>
-      </c>
-      <c r="E537" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>AZT, 3TC, ABC, TDF, EFV, NVP, ATV, RTV, LPV, DTG</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E538" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E539" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>Capsid, CA</t>
-        </is>
-      </c>
-      <c r="E540" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>USA, Dominican Republic</t>
-        </is>
-      </c>
-      <c r="E541" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
-      <c r="E542" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E543" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E544" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E545" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E546" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E547" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI, CAI</t>
-        </is>
-      </c>
-      <c r="E548" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI, CAI</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>Emtricitabine/tenofovir alafenamide (F/TAF), TAF, bicegravir, LEN</t>
-        </is>
-      </c>
-      <c r="E549" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="E550" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>2018-2023</t>
-        </is>
-      </c>
-      <c r="E551" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>2018-2023</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E552" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E553" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>Sanger (not stated)</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E554" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="E555" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E556" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E557" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>NRTI,NNRTI,PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>AZT, D4T, TDF, ABC</t>
-        </is>
-      </c>
-      <c r="E558" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>PV187006</t>
-        </is>
-      </c>
-      <c r="E559" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>PV187006</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>Near full length genome</t>
-        </is>
-      </c>
-      <c r="E560" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E561" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E562" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E563" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E564" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>Plasma; Whole Blood</t>
-        </is>
-      </c>
-      <c r="E565" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E566" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>INSTI, NRTI</t>
-        </is>
-      </c>
-      <c r="E567" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr"/>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>BIC, FTC, TAF</t>
-        </is>
-      </c>
-      <c r="E568" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E569" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E570" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E571" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>Protease, PR</t>
-        </is>
-      </c>
-      <c r="E572" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E573" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E574" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E575" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="E576" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>Derunavir (DRV)</t>
-        </is>
-      </c>
-      <c r="E577" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>No (Published sequences only)</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E578" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>Yes (recombinant clones)</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>PQ735970-PQ735985</t>
-        </is>
-      </c>
-      <c r="E579" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>PQ735970–PQ735985</t>
-        </is>
-      </c>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>Reverse transcriptase, RT; Protease, PR</t>
-        </is>
-      </c>
-      <c r="E580" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>China, United States</t>
-        </is>
-      </c>
-      <c r="E581" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>1978-2023</t>
-        </is>
-      </c>
-      <c r="E582" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E583" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E584" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E585" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>8654, 10551</t>
-        </is>
-      </c>
-      <c r="E586" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E587" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E588" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
-        </is>
-      </c>
-      <c r="E589" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E590" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>PP280627 to PP280757</t>
-        </is>
-      </c>
-      <c r="E591" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>Reverse transcriptase, RT</t>
-        </is>
-      </c>
-      <c r="E592" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="E593" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>2017-2018</t>
-        </is>
-      </c>
-      <c r="E594" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>2017-2018</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E595" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>DBS; Whole Blood</t>
-        </is>
-      </c>
-      <c r="E596" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="E597" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E598" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
-        </is>
-      </c>
-      <c r="E599" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E600" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
-        </is>
-      </c>
-      <c r="E601" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="E602" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="E603" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E604" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>RT, PR, IN</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E605" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E606" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="E607" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E608" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E609" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
-        </is>
-      </c>
-      <c r="E610" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>Protease, Reverse transcriptase, Integrase, Capsid</t>
-        </is>
-      </c>
-      <c r="E611" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E612" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>Illumina sequencing</t>
-        </is>
-      </c>
-      <c r="E613" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E614" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>RT,PR,IN,CA</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E615" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E616" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E617" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
-        </is>
-      </c>
-      <c r="E618" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>NRTI, CAI</t>
-        </is>
-      </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>Emtricitabine (FTC), Tenofovir (TFV), Lamivudine (3TC), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
-        </is>
-      </c>
-      <c r="E619" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E620" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D621" t="inlineStr">
-        <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
-        </is>
-      </c>
-      <c r="E621" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>0 (Review paper)</t>
-        </is>
-      </c>
-      <c r="D622" t="inlineStr">
-        <is>
-          <t>Kenya, Uganda, Tanzania, Ethiopia</t>
-        </is>
-      </c>
-      <c r="E622" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>2015-2025</t>
-        </is>
-      </c>
-      <c r="E623" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
-      </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E624" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E625" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E626" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D627" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E627" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E451"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8944,2707 +8944,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>40391923</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>227</v>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>47</v>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Hair</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E349" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>1</v>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E351" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>2006-2024</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>RT, PR, IN</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E358" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>40431742</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
-      <c r="E359" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>40431742</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
-        </is>
-      </c>
-      <c r="E360" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>40490983</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E361" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>40573423</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E362" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>40573423</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>ATV/r, NFV, D4T, NVP, RAL</t>
-        </is>
-      </c>
-      <c r="E363" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>40596906</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
-        </is>
-      </c>
-      <c r="E364" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>Whole Blood</t>
-        </is>
-      </c>
-      <c r="E365" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
-        </is>
-      </c>
-      <c r="E366" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>40839365</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>212</v>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="E367" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>7 (Uncertain)</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="E368" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E369" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E370" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>0</v>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>9685</t>
-        </is>
-      </c>
-      <c r="E371" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E372" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>2004-2021</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E373" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E374" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E375" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E376" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
-        </is>
-      </c>
-      <c r="E377" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E378" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INST</t>
-        </is>
-      </c>
-      <c r="E379" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E380" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>0</v>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E381" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes  </t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E382" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Envelope; Integrase; Near full length genome</t>
-        </is>
-      </c>
-      <c r="E383" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>Sanger, NGS</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>Illumina sequencing</t>
-        </is>
-      </c>
-      <c r="E384" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
-      </c>
-      <c r="E385" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>INSTI</t>
-        </is>
-      </c>
-      <c r="E386" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>Dolutegravir (DTG)</t>
-        </is>
-      </c>
-      <c r="E387" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E388" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C389" t="n">
-        <v>0</v>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E389" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>Protease, PR; Gag</t>
-        </is>
-      </c>
-      <c r="E390" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E391" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E392" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E393" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>INSTI, PI, NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E394" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
-        </is>
-      </c>
-      <c r="E395" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C396" t="n">
-        <v>223</v>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="E396" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>NGS</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E397" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>PBMC (Whole blood OK)</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>Whole Blood</t>
-        </is>
-      </c>
-      <c r="E398" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E399" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>INSTI, NRTI</t>
-        </is>
-      </c>
-      <c r="E400" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E401" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>Full genome</t>
-        </is>
-      </c>
-      <c r="E402" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
-      <c r="E403" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E404" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E405" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>Yes (Only past sequences)</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E406" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E407" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>PR, RT, IN (presumably)</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E408" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>Plasma (presumably)</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E409" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E410" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E411" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>RT,IN</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>Integrase, IN</t>
-        </is>
-      </c>
-      <c r="E412" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>DTG (no other ARVs specified)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
-        </is>
-      </c>
-      <c r="E413" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E414" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C415" t="n">
-        <v>10</v>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="E415" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>USA, Dominican Republic</t>
-        </is>
-      </c>
-      <c r="E416" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
-      <c r="E417" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E418" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E419" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E420" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>AZT, D4T, TDF, ABC</t>
-        </is>
-      </c>
-      <c r="E421" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E422" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>Near full length genome</t>
-        </is>
-      </c>
-      <c r="E423" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>INSTI, NRTI</t>
-        </is>
-      </c>
-      <c r="E424" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>BIC, FTC, TAF</t>
-        </is>
-      </c>
-      <c r="E425" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E426" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E427" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C428" t="n">
-        <v>0</v>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E428" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E429" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="E430" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>Derunavir (DRV)</t>
-        </is>
-      </c>
-      <c r="E431" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>No (Published sequences only)</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E432" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C433" t="n">
-        <v>0</v>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>8654, 10551</t>
-        </is>
-      </c>
-      <c r="E433" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>China, United States</t>
-        </is>
-      </c>
-      <c r="E434" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>1978-2023</t>
-        </is>
-      </c>
-      <c r="E435" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E436" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E437" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="E438" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> No</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E439" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E440" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
-        </is>
-      </c>
-      <c r="E441" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>PP280627 to PP280757</t>
-        </is>
-      </c>
-      <c r="E442" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E443" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
-        </is>
-      </c>
-      <c r="E444" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C445" t="n">
-        <v>64</v>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E445" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E446" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E447" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E448" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>2015-2025</t>
-        </is>
-      </c>
-      <c r="E449" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E450" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -832,14 +832,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI</t>
@@ -857,14 +853,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
@@ -882,7 +874,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -907,14 +899,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
@@ -932,14 +920,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>ATV/r, NFV, D4T, NVP, RAL</t>
@@ -957,7 +941,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -982,7 +966,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1007,7 +991,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1032,7 +1016,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1055,7 +1039,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1080,7 +1064,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1130,11 +1114,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0 (Review paper)</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1153,7 +1139,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1178,7 +1164,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1203,7 +1189,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1228,7 +1214,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1253,7 +1239,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1278,14 +1264,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
@@ -1303,14 +1285,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
@@ -1328,14 +1306,10 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INST</t>
@@ -1378,7 +1352,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1426,7 +1400,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1451,7 +1425,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1476,14 +1450,10 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>PBMC</t>
@@ -1501,14 +1471,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>INSTI</t>
@@ -1526,14 +1492,10 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>Dolutegravir (DTG)</t>
@@ -1576,7 +1538,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1599,7 +1561,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1586,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1649,7 +1611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1674,7 +1636,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1699,14 +1661,10 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>INSTI, PI, NRTI, NNRTI</t>
@@ -1724,14 +1682,10 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
@@ -1749,7 +1703,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1772,7 +1726,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1797,7 +1751,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,7 +1776,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1847,7 +1801,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1872,7 +1826,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1897,14 +1851,10 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
@@ -1922,14 +1872,10 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
@@ -1972,7 +1918,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1997,7 +1943,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2022,7 +1968,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2047,7 +1993,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2072,7 +2018,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2097,7 +2043,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2122,7 +2068,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2172,7 +2118,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2195,7 +2141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2220,7 +2166,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2245,7 +2191,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2270,7 +2216,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2295,7 +2241,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2320,7 +2266,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2370,14 +2316,10 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>INSTI, NRTI</t>
@@ -2395,14 +2337,10 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>BIC, FTC, TAF</t>
@@ -2470,7 +2408,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2518,14 +2456,10 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>PI</t>
@@ -2543,14 +2477,10 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>Derunavir (DRV)</t>
@@ -2593,7 +2523,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2616,7 +2546,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2641,7 +2571,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2691,7 +2621,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2716,14 +2646,10 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Plasma</t>
@@ -2741,7 +2667,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2766,12 +2692,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2791,14 +2717,10 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
@@ -2816,7 +2738,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2841,14 +2763,10 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>NRTI, NNRTI</t>
@@ -2866,14 +2784,10 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
@@ -2891,7 +2805,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2939,7 +2853,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2989,7 +2903,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3014,7 +2928,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3039,14 +2953,10 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PBMC (Whole blood OK)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1796,22 +1796,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>2015-2021</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1826,17 +1826,13 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2015-2021</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1851,13 +1847,13 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1867,18 +1863,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1968,17 +1968,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2013,22 +2013,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2063,22 +2063,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2093,17 +2093,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>10</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2118,15 +2116,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>10</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2211,22 +2211,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2241,17 +2241,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>AZT, D4T, TDF, ABC</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2261,22 +2261,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2291,17 +2291,13 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2316,13 +2312,13 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2332,18 +2328,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2383,17 +2383,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2408,15 +2406,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2431,17 +2431,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2456,13 +2452,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2472,18 +2468,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>No (Published sequences only)</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Derunavir (DRV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2498,17 +2498,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>No (Published sequences only)</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8654, 10551</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2523,15 +2521,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>8654, 10551</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978-2023</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1978-2023</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2621,17 +2621,13 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2646,13 +2642,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> No</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2692,17 +2692,13 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> None</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2712,18 +2708,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PP280627- PP280757</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
+          <t>PP280627 to PP280757</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2738,17 +2738,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2763,13 +2759,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2779,18 +2775,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>64</v>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2805,15 +2803,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>64</v>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Yes (PrEP)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2848,22 +2848,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -2928,41 +2928,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,22 +986,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>212</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1011,7 +1009,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1019,12 +1017,14 @@
           <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>212</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1059,22 +1059,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0 (Review paper)</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1239,17 +1239,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1259,18 +1255,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1285,13 +1281,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1301,18 +1297,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1327,17 +1327,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1352,15 +1350,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes  </t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Envelope; Integrase; Near full length genome</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1400,17 +1400,13 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Envelope; Integrase; Near full length genome</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1425,17 +1421,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Sanger, NGS</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Illumina sequencing</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1450,13 +1442,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1466,18 +1458,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1487,18 +1483,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG)</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1513,17 +1511,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Protease, PR; Gag</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1538,15 +1536,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Protease, PR; Gag</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1611,17 +1611,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, PI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1636,17 +1632,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1656,18 +1648,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>223</v>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTI, PI, NRTI, NNRTI</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1677,18 +1671,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1703,15 +1701,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>223</v>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1746,22 +1746,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2015-2021</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1771,7 +1771,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1779,14 +1779,10 @@
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1801,17 +1797,13 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2015-2021</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1821,18 +1813,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1842,18 +1838,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1963,22 +1963,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -1988,22 +1988,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2013,22 +2013,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>RT,IN</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2038,22 +2036,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2068,17 +2066,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2093,15 +2091,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>10</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2136,22 +2136,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2161,7 +2161,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2186,22 +2186,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma (not stated)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>AZT, D4T, TDF, ABC</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2236,22 +2236,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2266,17 +2266,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2291,13 +2287,13 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2307,18 +2303,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2358,17 +2358,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2383,15 +2381,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2406,17 +2406,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2431,13 +2427,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2447,18 +2443,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>No (Published sequences only)</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Derunavir (DRV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2473,17 +2473,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>No (Published sequences only)</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8654, 10551</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2498,15 +2496,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8654, 10551</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978-2023</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1978-2023</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2596,17 +2596,13 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2621,13 +2617,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2642,17 +2642,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> No</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2667,17 +2667,13 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> None</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2687,18 +2683,18 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2713,17 +2709,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2733,18 +2725,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>64</v>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2754,18 +2748,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2780,15 +2778,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>64</v>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2798,22 +2798,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2823,22 +2823,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2878,66 +2878,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,20 +481,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40391923</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>47</v>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, RAL</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>Dolutegravir (DTG), Tenofovir (TFV), Lamivudine (3TC), Darunavir (DRV)</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -509,17 +511,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>47</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -534,17 +534,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hair</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -559,17 +559,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -579,22 +579,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Not reported</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -609,11 +609,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -632,13 +634,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RT, PR, IN</t>
+          <t>2006-2024</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>RT, PR, IN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -827,18 +827,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -853,13 +857,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -869,22 +873,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -894,18 +894,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -915,7 +919,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -923,10 +927,14 @@
           <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATV/r, NFV, D4T, NVP, RAL</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -936,22 +944,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -961,22 +965,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>ATV/r, NFV, D4T, NVP, RAL</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -986,20 +986,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>212</v>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1009,22 +1011,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1034,22 +1036,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1059,22 +1061,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1084,7 +1084,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0 (Review paper)</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1109,22 +1109,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1134,22 +1134,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>TAF, FTC, TDF, 3TC, DTG, BIC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1214,17 +1214,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1239,13 +1239,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1255,18 +1259,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1276,18 +1284,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1297,22 +1309,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1322,20 +1334,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1345,22 +1355,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes  </t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1370,22 +1376,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Envelope; Integrase; Near full length genome</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1400,13 +1402,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1421,13 +1427,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1442,13 +1450,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes  </t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1458,22 +1470,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Envelope; Integrase; Near full length genome</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1483,20 +1495,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Illumina sequencing</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1506,22 +1520,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Protease, PR; Gag</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1531,22 +1541,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1556,22 +1562,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1586,7 +1588,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1611,13 +1613,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTI, PI, NRTI, NNRTI</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1632,13 +1636,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
+          <t>Protease, PR; Gag</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1648,20 +1656,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>223</v>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1671,22 +1681,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1696,22 +1706,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1721,7 +1731,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1729,14 +1739,10 @@
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>INSTI, PI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1746,22 +1752,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2015-2021</t>
+          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1771,18 +1773,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>223</v>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1792,18 +1796,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1813,22 +1821,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>PBMC (Whole blood OK)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1838,22 +1846,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1863,22 +1871,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1888,7 +1896,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1898,12 +1906,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>2015-2021</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1913,22 +1921,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1938,22 +1942,18 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -1963,22 +1963,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -1988,22 +1988,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2013,20 +2013,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>10</v>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2036,22 +2038,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2061,22 +2063,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2086,17 +2088,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2111,22 +2113,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2136,22 +2138,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2161,22 +2163,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Sanger (not stated)</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2186,22 +2186,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plasma (not stated)</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2211,22 +2211,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2236,22 +2236,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2261,18 +2261,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2282,7 +2286,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2290,10 +2294,14 @@
           <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TAF, FTC, LEN, BIC</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>Emtricitabine/tenofovir alafenamide (F/TAF), TAF, bicegravir, LEN</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2303,22 +2311,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2328,22 +2336,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2353,20 +2361,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Plasma (not stated)</t>
+        </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2376,22 +2386,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, D4T, TDF, ABC</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2401,18 +2411,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2422,18 +2436,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Derunavir (DRV)</t>
+          <t>Near full length genome</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2443,22 +2461,18 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>No (Published sequences only)</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2468,20 +2482,18 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8654, 10551</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2491,22 +2503,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2516,22 +2528,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1978-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2541,22 +2553,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2566,22 +2576,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2591,18 +2601,18 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2612,22 +2622,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> No</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Derunavir (DRV)</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2642,17 +2648,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>No (Published sequences only)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2667,13 +2673,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
+          <t>8654, 10551</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2683,18 +2691,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2704,18 +2716,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+          <t>1978-2023</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2725,20 +2741,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>64</v>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2748,22 +2766,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2773,22 +2791,18 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2798,17 +2812,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve"> No</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2823,22 +2837,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2848,22 +2862,18 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2873,21 +2883,236 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>64</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TDF, TAF, FTC, LEN</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Emtricitabine (FTC), Tenofovir (TFV), Lamivudine (3TC), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2015-2025</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
-      <c r="E103" t="n">
+      <c r="E112" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,32 +446,34 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT-200 Answer</t>
+          <t>Llama3.1-70B FT Answer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT-200 Correct</t>
+          <t>Llama3.1-70B FT Correct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>18715920</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>227</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -481,22 +483,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, RAL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Tenofovir (TFV), Lamivudine (3TC), Darunavir (DRV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -506,20 +508,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>47</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -529,22 +533,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -554,17 +558,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -579,12 +583,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>25637519</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -604,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>26246578</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -629,7 +633,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -637,12 +641,14 @@
           <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -652,22 +658,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -677,22 +683,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -702,22 +708,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RT, PR, IN</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -727,22 +733,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -752,22 +758,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -777,22 +783,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -802,22 +808,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TFV, FTC, RAL, DTG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Raltegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -827,22 +833,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -852,18 +858,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -873,18 +883,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>Tenofovir, Lamivudine, Nevirapine, Efavirenz, Etravirine, Rilpivirine</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -894,12 +908,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -919,22 +933,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -944,18 +958,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -965,18 +983,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ATV/r, NFV, D4T, NVP, RAL</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -986,22 +1008,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1011,22 +1033,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1036,22 +1058,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1061,7 +1083,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1069,12 +1091,14 @@
           <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>212</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1084,22 +1108,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1109,22 +1133,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1134,22 +1158,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TAF, FTC, TDF, 3TC, DTG, BIC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1159,22 +1183,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1184,22 +1208,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0 (Review paper)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1209,22 +1233,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1234,22 +1258,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1259,22 +1283,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1284,22 +1308,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1309,12 +1333,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1324,7 +1348,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1334,18 +1358,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1355,18 +1383,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1376,18 +1408,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INSTI, NNRTI</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1397,22 +1433,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1422,20 +1458,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1445,22 +1483,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1470,22 +1508,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RT, IN, NC, Env</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Envelope; Integrase; Near full length genome</t>
+          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1495,22 +1533,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Illumina sequencing</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1520,18 +1558,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1541,18 +1583,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1562,18 +1608,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1583,22 +1633,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1608,20 +1658,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1631,22 +1683,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Protease, PR; Gag</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1656,22 +1708,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1681,22 +1733,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1706,22 +1758,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1731,18 +1783,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTI, PI, NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1752,18 +1808,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NRTI, PI, NNRTI, INSTI</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1773,20 +1833,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>223</v>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TDF,FTC,EVG</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1796,22 +1858,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1821,22 +1883,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PBMC (Whole blood OK)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1846,7 +1908,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1856,12 +1918,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1871,22 +1933,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1896,22 +1958,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2015-2021</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1921,18 +1983,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1942,18 +2008,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -1963,17 +2033,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1988,22 +2058,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2013,22 +2083,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2038,22 +2108,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2063,7 +2133,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2073,12 +2143,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2088,22 +2158,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2113,22 +2183,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2138,22 +2208,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2163,20 +2233,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>10</v>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2186,22 +2258,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2211,22 +2283,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2236,22 +2308,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2261,17 +2333,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2286,22 +2358,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TAF, FTC, LEN, BIC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Emtricitabine/tenofovir alafenamide (F/TAF), TAF, bicegravir, LEN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2311,22 +2383,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2336,22 +2408,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2361,22 +2433,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plasma (not stated)</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2386,22 +2458,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2411,17 +2483,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2436,22 +2508,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Whole genome</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Near full length genome</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2461,18 +2533,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2482,18 +2558,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2503,22 +2583,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2528,22 +2608,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2553,20 +2633,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2576,22 +2658,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2601,18 +2683,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2622,18 +2708,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NNRTI, NRTI, PI</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Derunavir (DRV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2643,7 +2733,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2653,12 +2743,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No (Published sequences only)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2668,7 +2758,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2676,12 +2766,14 @@
           <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>0</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8654, 10551</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2691,22 +2783,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2716,22 +2808,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1978-2023</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2741,12 +2833,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2766,22 +2858,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2791,18 +2883,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2812,22 +2908,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> No</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2837,22 +2933,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2862,18 +2958,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2883,18 +2983,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -2904,18 +3008,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -2925,20 +3033,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>64</v>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -2948,17 +3058,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2973,22 +3083,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN, Env</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -2998,22 +3108,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TDF, TAF, FTC, LEN</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Emtricitabine (FTC), Tenofovir (TFV), Lamivudine (3TC), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3023,22 +3133,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37042390</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3048,22 +3158,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37042390</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>RAL, DRV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3073,17 +3183,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3098,21 +3208,3325 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37104815</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Whole Blood, Semen</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Plasma; PBMC; Semen</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37147875</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37147875</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>37279764</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Whole Blood</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CAB, RPV</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>37376649</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Plasma; PBMC</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>37376649</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>37376649</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>37376649</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>37439411</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>9387</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>14969</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>37495103</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>37495103</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, EFV, ABC, DTG, LPV/r, ETR</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, Illumina sequencing</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Next-generation sequencing (NGS)</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>37515095</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3TC, ABC, AZT, D4T, DDI, FTC, TDF, ETR, EFV, NVP, RPV</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Emtricitabine (FTC), Tenofovir (TDF), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>25 or 30</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, Illumina sequencing, Oxford nanopore</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Oxford Nanopore sequencing</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>37546367</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>37546367</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>37546367</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>37574435</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>70 or 79</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>37574435</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DTG, BIC, FTC, TAF</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>37585352</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>37585352</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EFV, FTC, TDF, 3TC, NVP, AZT</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Rilpivirine (RPV)</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>57902</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>57802</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>37632026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, EFV, NVP, LPV/r, ATV/r</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>37674678</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>37775947</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NFLG, Envelope</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Envelope</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>gp120</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, EFV</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>704 or 106</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>820 or 46</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2019-2022</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
-      <c r="E112" t="n">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>37941373</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>37941373</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Full genome, NFLG</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Pol, Env</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>NRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, NGS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>37993493</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>37993493</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Dolutegravir</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>RTI, PI</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2020, 2022, 2023</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2012, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, NGS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>CSF, Plasma</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, LPV, EFV</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Plasma, PBMC</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF, EVG</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -763,17 +763,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -788,17 +788,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>TFV, FTC, RAL, DTG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -813,17 +813,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TFV, FTC, RAL, DTG</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raltegravir, Dolutegravir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -838,17 +838,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -863,7 +863,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Tenofovir, Lamivudine, Nevirapine, Efavirenz, Etravirine, Rilpivirine</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -888,17 +888,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Nevirapine, Efavirenz, Etravirine, Rilpivirine</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1063,17 +1063,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2263,17 +2263,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Env</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>PR, RT, IN, Env</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3213,17 +3213,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Whole Blood, Semen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma; PBMC; Semen</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Plasma; PBMC; Semen</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3838,17 +3838,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>25 or 30</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>25 or 30</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4313,17 +4313,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4363,17 +4363,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>EFV, FTC, TDF, 3TC, NVP, AZT</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4388,17 +4388,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>EFV, FTC, TDF, 3TC, NVP, AZT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Rilpivirine (RPV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>57802</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>57802</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TDF, 3TC, EFV</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019-2022</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>921</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>NRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Pol, Env</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pol, Env</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5713,17 +5713,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Dolutegravir</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Dolutegravir</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2012, 2020, 2022</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5963,17 +5963,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2020, 2022, 2023</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2012, 2020, 2022</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6038,17 +6038,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CSF, Plasma</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CSF, Plasma</t>
+          <t>TDF, 3TC, LPV, EFV</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6188,17 +6188,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TDF, 3TC, LPV, EFV</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6438,17 +6438,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT Answer</t>
+          <t>Llama3.1-70B FT-200 Answer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT Correct</t>
+          <t>Llama3.1-70B FT-200 Correct</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,22 +483,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19104010</t>
+          <t>18715920</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -508,22 +508,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19104010</t>
+          <t>18715920</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,22 +533,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21115794</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -558,22 +558,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23749954</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -583,22 +583,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25637519</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26246578</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>LPV, atazanavir, nelfinavir, EFV, TDF, AZT, FTC, 3TC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -633,22 +633,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27009474</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -658,22 +658,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -683,22 +683,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -708,22 +708,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -733,22 +733,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -758,7 +758,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>24227862</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -783,7 +783,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>24227862</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TFV, FTC, RAL, DTG</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raltegravir, Dolutegravir</t>
+          <t>ETR, RPV, NVP, EFV</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -808,22 +808,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>25637519</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -833,7 +833,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>25637519</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>25637519</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Nevirapine, Efavirenz, Etravirine, Rilpivirine</t>
+          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Zidovudine, Abacavir sulphate, Lamivudine, Emtricitabine, Tenofovir disoproxil fumarate</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -883,22 +883,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>26246578</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -908,22 +908,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>26246578</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RAL, EVG, DTG</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -933,22 +933,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -958,22 +958,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -983,22 +983,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1008,22 +1008,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1033,22 +1033,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1058,22 +1058,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>26559830</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1083,22 +1083,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>26559830</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Amprenavir (APV), Atazanavir (ATV), Darunavir (DRV), Indinavir (IDV), Lopinavir (LPV), Nelfinavir (NFV), Ritonavir (RTV), Saquinavir (SQV), Tipranavir (TPV)</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1108,22 +1108,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1133,22 +1133,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1158,22 +1158,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1183,7 +1183,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1208,22 +1208,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1233,22 +1233,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, 3TC, LPV</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1258,22 +1258,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1283,22 +1283,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1308,22 +1308,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1333,22 +1333,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1358,22 +1358,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1383,22 +1383,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Tenofovir alafenamide</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1408,22 +1408,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1433,22 +1433,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30803972</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1458,22 +1458,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>30803972</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1483,22 +1483,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>30803972</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1508,22 +1508,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1533,22 +1533,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1558,22 +1558,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1583,22 +1583,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1608,22 +1608,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1633,22 +1633,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1658,22 +1658,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1683,22 +1683,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1708,7 +1708,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1733,7 +1733,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lamivudine, Islatravir, Doravirine, Rilpivirine</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1758,22 +1758,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1783,22 +1783,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1808,22 +1808,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1833,22 +1833,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir (DTG), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1858,12 +1858,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1883,12 +1883,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1908,12 +1908,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1933,22 +1933,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1958,22 +1958,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1983,22 +1983,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2008,22 +2008,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2033,22 +2033,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2058,22 +2058,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2083,17 +2083,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2108,22 +2108,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2133,22 +2133,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2158,22 +2158,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2183,22 +2183,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2208,22 +2208,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2233,7 +2233,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2258,22 +2258,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36519389</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2283,22 +2283,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36519389</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2308,22 +2308,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>36519389</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2333,22 +2333,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2358,22 +2358,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2383,22 +2383,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir (DTG), Bictegravir (BIC), Raltegravir (RAL), Elvitegravir(EVG), Tenofovir (TFV), Abacavir (ABC), Lamivudine (3TC), Emtricitabine(FTC)</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2408,12 +2408,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2433,22 +2433,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2458,22 +2458,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2483,22 +2483,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2508,22 +2508,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2533,17 +2533,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2558,17 +2558,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2583,22 +2583,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2608,7 +2608,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2633,22 +2633,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2658,22 +2658,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RPV</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2683,22 +2683,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2708,22 +2708,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36851760</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NNRTI, NRTI, PI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2733,7 +2733,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2758,17 +2758,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2783,12 +2783,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2808,22 +2808,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2833,22 +2833,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2858,7 +2858,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3TC, TDF, EFV, LPV/r</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2883,17 +2883,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2908,22 +2908,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2933,22 +2933,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36961945</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2958,22 +2958,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2983,22 +2983,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3008,22 +3008,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>36751650</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3033,22 +3033,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>36751650</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Stavudine (D4T), Emtricitabine(FTC), Lamivudine (3TC), Tenofovir (TFV), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Amprenavir (APV), Nelfinavir (NFV), Tipranavir (TPV), Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir(EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3058,22 +3058,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3083,22 +3083,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3108,22 +3108,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Env</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3133,7 +3133,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37042390</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3158,7 +3158,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37042390</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>RAL, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir, Tenofovir, Zidovudine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3183,22 +3183,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Atazanavir (ATV), Lopinavir (LPV), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3208,22 +3208,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Plasma; PBMC; Semen</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3233,22 +3233,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3258,22 +3258,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3283,22 +3283,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3308,17 +3308,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3333,17 +3333,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3358,22 +3358,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3383,22 +3383,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3408,22 +3408,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3433,22 +3433,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3458,22 +3458,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lamivudine (3TC), Emtricitabine (FTC)</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3483,22 +3483,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3508,22 +3508,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3533,22 +3533,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3558,22 +3558,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>36982978</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3583,22 +3583,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>36982978</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3608,22 +3608,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>36982978</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3633,22 +3633,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>36982978</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3658,22 +3658,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>LPV, ATV, EFV, NVP, 3TC, ABC, AZT, FTC, D4T, TDF</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>Abacavir, Lamivudine, Emtricitabine, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Ritonavir-boosted lopinavir, Ritonavir-boosted atazanavir</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3683,22 +3683,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3708,22 +3708,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV, ABC, DTG, LPV/r, ETR</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3733,22 +3733,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (NGS)</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3758,22 +3758,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3783,22 +3783,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Envelope</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3808,22 +3808,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>37042390</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3TC, ABC, AZT, D4T, DDI, FTC, TDF, ETR, EFV, NVP, RPV</t>
+          <t>85 or (40 and 38)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Emtricitabine (FTC), Tenofovir (TDF), Efavirenz (EFV)</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3833,22 +3833,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37052343</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3858,22 +3858,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37052343</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3883,22 +3883,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37052343</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3908,22 +3908,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37052343</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>25 or 30</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2014-2020</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3933,7 +3933,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing, Oxford nanopore</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Oxford Nanopore sequencing</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3958,22 +3958,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3983,22 +3983,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4008,22 +4008,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4033,22 +4033,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37085698</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4058,22 +4058,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37085698</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4083,17 +4083,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4108,22 +4108,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4133,22 +4133,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Emtricitabine (FTC), Lamivudine (3TC), Tenofovir (TFV), Stavudine (D4T), Didanosine (DDI), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Atazanavir (ATV), Darunavir (DRV), Lopinavir'(LPV), Fosamprenavir (FPV), Indinavir (IDV), Nelfinavir (NFV), Saquinavir (SQV), Tipranavir (TPV), Bictegravir (BIC), Cabotegravir (CAB), Dolutegravir (DTG), Elvitegravir (EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4158,22 +4158,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4183,22 +4183,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI; NRTI</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4208,22 +4208,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir (DTG); Emtricitabine (FTC); Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4233,22 +4233,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4258,22 +4258,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Didanosine, Abacavir (ABC), Zidovudine (ZDV), Stavudine (d4T), Delavirdine (DLV), Nevirapine (NVP), Efavirenz (EFV), Nelfinavir, Elvitegravir (EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4283,22 +4283,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4308,22 +4308,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>37574435</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4333,22 +4333,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>37574435</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Nevirapine, Efavirenz, Nelfinavir, Indinavir, Darunavir</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4358,22 +4358,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>37585352</t>
+          <t>37327289</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>EFV, FTC, TDF, 3TC, NVP, AZT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Rilpivirine (RPV)</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4383,22 +4383,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>37585352</t>
+          <t>37327289</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NVP, EFV, ETR, 3TC, ABC, AZT, TDF</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4408,17 +4408,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4433,22 +4433,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>57802</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4458,22 +4458,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AZT, 3TC, TDF, EFV, NVP, LPV/r, ATV/r</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4483,22 +4483,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4508,22 +4508,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4533,22 +4533,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4558,22 +4558,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine (ZDV), Tenofovir (TFV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4583,22 +4583,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Plasma; PBMC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4608,22 +4608,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4633,22 +4633,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Lamivudine (3TC), Tenofovir (TFV), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Stavudine (D4T), Emtricitabine(FTC)</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4658,22 +4658,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4683,22 +4683,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4708,22 +4708,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tenofovir (TFV), Zidovudine'(AZT), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP)</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4733,22 +4733,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4758,22 +4758,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4783,22 +4783,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4808,22 +4808,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Lopinavir (LPV), Ritonavir (RTV), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4833,22 +4833,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4858,7 +4858,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4883,22 +4883,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4908,22 +4908,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>704 or 106</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4933,22 +4933,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4958,22 +4958,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>3TC, ABC, AZT, D4T, DDI, FTC, TDF, ETR, EFV, NVP, RPV</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>FTC, TDF, EFV</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4983,22 +4983,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -5008,22 +5008,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5033,12 +5033,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5058,22 +5058,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5083,22 +5083,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5108,12 +5108,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5133,22 +5133,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5158,22 +5158,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5183,22 +5183,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>atazanavir, fosamprenavir, indinavir, saquinavir, nelfinavir, abacavir, didanosine, emtricitabine, lamivudine, azidothymidine, stavudine, tenofovir, doravirine, etravirine, nevirapine, rilpivirine, efavirenz, etravirine</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5208,22 +5208,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5233,22 +5233,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5258,22 +5258,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5283,22 +5283,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>37941373</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5308,22 +5308,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>37941373</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5333,7 +5333,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Lopinavir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5358,7 +5358,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5383,22 +5383,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5408,22 +5408,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5433,22 +5433,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5458,12 +5458,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5483,22 +5483,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Pol, Env</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5508,22 +5508,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NNRTI, PI, NRTI</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5533,22 +5533,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5558,7 +5558,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5583,22 +5583,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5608,22 +5608,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5633,22 +5633,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5658,17 +5658,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5708,22 +5708,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Dolutegravir</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5733,22 +5733,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5758,22 +5758,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5783,22 +5783,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5808,22 +5808,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5833,22 +5833,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5858,22 +5858,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>37585352</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>RTI, PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5883,22 +5883,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5908,22 +5908,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5933,22 +5933,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5958,22 +5958,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2012, 2020, 2022</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5983,22 +5983,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6008,22 +6008,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6033,22 +6033,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37632026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Lamivudine (3TC), Stavudine (D4T), Tenofovir (TDF), Abacavir (ABC), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV)</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6058,22 +6058,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CSF, Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6083,22 +6083,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bictegravir (BIC), Emtricitabine(FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6108,22 +6108,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37649807</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6133,22 +6133,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37649807</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tenofovir disoproxil fumarate (TDF), Lamivudine (3TC), Emtricitabine (FTC), NNRTI, Dolutegravir (DTG), Protease-inhibitor (PI)</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6158,22 +6158,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37662576</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TDF, 3TC, LPV, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6183,22 +6183,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37662576</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Darunavir, Lopinavir</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6208,22 +6208,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37662576</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Protease, PR</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6233,22 +6233,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6258,22 +6258,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TPV, D4T, AZT, ETR, RPV, NVP, EFV</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6283,12 +6283,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6308,17 +6308,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6333,22 +6333,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6358,22 +6358,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6383,22 +6383,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6408,22 +6408,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6433,22 +6433,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6458,22 +6458,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6483,22 +6483,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir, Tenofovir, Lamivudine</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6508,25 +6508,2425 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t>37775947</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>37775947</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INST</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>37775947</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>37775947</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>South America, Africa, USA</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Serum, Plasma, DBS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DBS</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NFLG, Envelope</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Envelope</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>gp120</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>37880705</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>37880705</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Stavudine (d4T), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV), Nelfinavir (NFV), Atazanavir (ATV), Lopinavir (LPV), Amprenavir (APV), Saquinavir (SQV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT; Protease, PR</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>37910452</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>37910452</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>37920909</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>37920909</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>RAL, EVG, DTG, BIC, CAB</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>820 or 46</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>37941373</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Plasma, PBMC</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>37966701</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>INSTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>37966701</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>cabotegravir, rilpivirine</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>37973713</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, NGS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>37993493</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>37993493</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>38022124</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>INSTI, NRTI</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>38022124</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>38031075</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>38031075</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Lamivudine, Tenofovir, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NVP</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2015-2019</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2020, 2022, 2023</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Integrase, IN</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>CSF, Plasma</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CSF</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
           <t>38090027</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>38140649</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>38140649</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>INSTI; NRTI; NNRTI; PI</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>38140667</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
         <is>
           <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E244" t="n">
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>38142692</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>38152686</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2008-2019</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Gag, Pol, Env, Nef, vpu</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Envelope; Full genome; Near full length genome</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Islatravir (ISL), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,17 +688,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -938,17 +938,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -963,17 +963,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -988,17 +988,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT</t>
+          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NRTI, PI</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZT, 3TC, LPV</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>AZT, 3TC, LPV</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1283,22 +1283,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1333,22 +1333,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1408,22 +1408,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>30803972</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1483,22 +1483,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>30803972</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1633,22 +1633,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1683,22 +1683,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Lamivudine, Islatravir, Doravirine, Rilpivirine</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1733,22 +1733,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lamivudine, Islatravir, Doravirine, Rilpivirine</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1808,12 +1808,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>34516245</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV)</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1858,22 +1858,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2033,22 +2033,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2058,22 +2058,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2133,22 +2133,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2158,22 +2158,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2183,22 +2183,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36415058</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI, PI</t>
+          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2208,22 +2208,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>36519389</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2233,22 +2233,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>36519389</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI</t>
+          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2283,22 +2283,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>36519389</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2308,22 +2308,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36519389</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dolutegravir (DTG), Bictegravir (BIC), Raltegravir (RAL), Elvitegravir(EVG), Tenofovir (TFV), Abacavir (ABC), Lamivudine (3TC), Emtricitabine(FTC)</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2358,22 +2358,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2383,22 +2383,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Bictegravir (BIC), Raltegravir (RAL), Elvitegravir(EVG), Tenofovir (TFV), Abacavir (ABC), Lamivudine (3TC), Emtricitabine(FTC)</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2413,17 +2413,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2458,22 +2458,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2483,22 +2483,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2508,22 +2508,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2683,22 +2683,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2708,22 +2708,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2738,17 +2738,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2808,22 +2808,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3TC, TDF, EFV, LPV/r</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2833,22 +2833,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2858,22 +2858,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2908,22 +2908,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2933,22 +2933,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2958,7 +2958,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36751650</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2983,7 +2983,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36751650</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Stavudine (D4T), Emtricitabine(FTC), Lamivudine (3TC), Tenofovir (TFV), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Amprenavir (APV), Nelfinavir (NFV), Tipranavir (TPV), Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir(EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3008,22 +3008,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36751650</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3033,22 +3033,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36751650</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Stavudine (D4T), Emtricitabine(FTC), Lamivudine (3TC), Tenofovir (TFV), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Amprenavir (APV), Nelfinavir (NFV), Tipranavir (TPV), Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir(EVG), Raltegravir (RAL)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3083,22 +3083,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3108,22 +3108,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Abacavir, Tenofovir, Zidovudine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3133,12 +3133,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>36795586</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Atazanavir (ATV), Lopinavir (LPV), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3158,7 +3158,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36795586</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Abacavir, Tenofovir, Zidovudine, Lamivudine, Dolutegravir</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3183,22 +3183,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Atazanavir (ATV), Lopinavir (LPV), Dolutegravir (DTG)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3208,12 +3208,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36851760</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3283,22 +3283,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>36920025</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3308,22 +3308,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>36920025</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3338,17 +3338,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3358,22 +3358,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3383,22 +3383,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Lamivudine (3TC), Emtricitabine (FTC)</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3458,22 +3458,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>36961945</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Emtricitabine (FTC)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3533,12 +3533,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>36982978</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
+          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3613,17 +3613,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3633,22 +3633,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>LPV, ATV, EFV, NVP, 3TC, ABC, AZT, FTC, D4T, TDF</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
+          <t>Abacavir, Lamivudine, Emtricitabine, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Ritonavir-boosted lopinavir, Ritonavir-boosted atazanavir</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3658,22 +3658,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>37017009</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LPV, ATV, EFV, NVP, 3TC, ABC, AZT, FTC, D4T, TDF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Abacavir, Lamivudine, Emtricitabine, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Ritonavir-boosted lopinavir, Ritonavir-boosted atazanavir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3758,22 +3758,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Envelope</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3783,22 +3783,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>37042390</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>85 or (40 and 38)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Envelope</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3808,7 +3808,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>37042390</t>
+          <t>37052343</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>85 or (40 and 38)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>2014-2020</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3908,12 +3908,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>37052343</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2014-2020</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -4008,12 +4008,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>37085698</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4058,22 +4058,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>37085698</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4083,22 +4083,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Emtricitabine (FTC), Lamivudine (3TC), Tenofovir (TFV), Stavudine (D4T), Didanosine (DDI), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Atazanavir (ATV), Darunavir (DRV), Lopinavir'(LPV), Fosamprenavir (FPV), Indinavir (IDV), Nelfinavir (NFV), Saquinavir (SQV), Tipranavir (TPV), Bictegravir (BIC), Cabotegravir (CAB), Dolutegravir (DTG), Elvitegravir (EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4133,22 +4133,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>37112971</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Emtricitabine (FTC), Lamivudine (3TC), Tenofovir (TFV), Stavudine (D4T), Didanosine (DDI), Doravirine (DOR), Efavirenz (EFV), Etravirine (ETR), Nevirapine (NVP), Rilpivirine (RPV), Atazanavir (ATV), Darunavir (DRV), Lopinavir'(LPV), Fosamprenavir (FPV), Indinavir (IDV), Nelfinavir (NFV), Saquinavir (SQV), Tipranavir (TPV), Bictegravir (BIC), Cabotegravir (CAB), Dolutegravir (DTG), Elvitegravir (EVG), Raltegravir (RAL)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI; NRTI</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>INSTI; NRTI</t>
+          <t>Dolutegravir (DTG); Emtricitabine (FTC); Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4208,12 +4208,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG); Emtricitabine (FTC); Tenofovir (TFV)</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Didanosine, Abacavir (ABC), Zidovudine (ZDV), Stavudine (d4T), Delavirdine (DLV), Nevirapine (NVP), Efavirenz (EFV), Nelfinavir, Elvitegravir (EVG), Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4258,12 +4258,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Didanosine, Abacavir (ABC), Zidovudine (ZDV), Stavudine (d4T), Delavirdine (DLV), Nevirapine (NVP), Efavirenz (EFV), Nelfinavir, Elvitegravir (EVG), Raltegravir (RAL)</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Nevirapine, Efavirenz, Nelfinavir, Indinavir, Darunavir</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4333,12 +4333,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>37327289</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Nevirapine, Efavirenz, Nelfinavir, Indinavir, Darunavir</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NVP, EFV, ETR, 3TC, ABC, AZT, TDF</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4383,22 +4383,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>37327289</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NVP, EFV, ETR, 3TC, ABC, AZT, TDF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4508,12 +4508,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INST</t>
+          <t>Abacavir (ABC), Zidovudine (ZDV), Tenofovir (TFV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4558,22 +4558,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine (ZDV), Tenofovir (TFV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Dolutegravir (DTG)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4658,22 +4658,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Tenofovir (TFV), Zidovudine'(AZT), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP)</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4708,22 +4708,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Zidovudine'(AZT), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP)</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4783,22 +4783,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Lopinavir (LPV), Ritonavir (RTV), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4808,22 +4808,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Lopinavir (LPV), Ritonavir (RTV), Efavirenz (EFV)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4883,22 +4883,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4913,17 +4913,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4938,17 +4938,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3TC, ABC, AZT, D4T, DDI, FTC, TDF, ETR, EFV, NVP, RPV</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>FTC, TDF, EFV</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4958,22 +4958,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3TC, ABC, AZT, D4T, DDI, FTC, TDF, ETR, EFV, NVP, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>FTC, TDF, EFV</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -5008,22 +5008,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5083,22 +5083,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2016-2017, 2019-2020</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5208,22 +5208,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5283,22 +5283,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Lopinavir, Dolutegravir, Raltegravir</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Lopinavir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5433,22 +5433,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5463,17 +5463,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5483,22 +5483,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI, PI, NRTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
+          <t>INSTI, NNRTI, PI, NRTI</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5583,22 +5583,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5613,17 +5613,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5713,17 +5713,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INST</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5833,22 +5833,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>37574435</t>
+          <t>37585352</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5858,12 +5858,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>37585352</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>67939</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5958,22 +5958,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -6008,22 +6008,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>37632026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Lamivudine (3TC), Stavudine (D4T), Tenofovir (TDF), Abacavir (ABC), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV)</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6033,22 +6033,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Lamivudine (3TC), Stavudine (D4T), Tenofovir (TDF), Abacavir (ABC), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV)</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Bictegravir (BIC), Emtricitabine(FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6083,12 +6083,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>37649807</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Emtricitabine(FTC), Tenofovir (TFV)</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Tenofovir disoproxil fumarate (TDF), Lamivudine (3TC), Emtricitabine (FTC), NNRTI, Dolutegravir (DTG), Protease-inhibitor (PI)</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6133,12 +6133,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>37649807</t>
+          <t>37662576</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Tenofovir disoproxil fumarate (TDF), Lamivudine (3TC), Emtricitabine (FTC), NNRTI, Dolutegravir (DTG), Protease-inhibitor (PI)</t>
+          <t>Protease, PR</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6208,22 +6208,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>37662576</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Protease, PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6283,12 +6283,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6408,22 +6408,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6433,22 +6433,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Dolutegravir, Tenofovir, Lamivudine</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6458,22 +6458,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37775947</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6483,12 +6483,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37775947</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Dolutegravir, Tenofovir, Lamivudine</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6513,17 +6513,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6533,22 +6533,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6558,22 +6558,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6583,22 +6583,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>South America, Africa, USA</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6608,22 +6608,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Envelope</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6633,22 +6633,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6658,22 +6658,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6683,22 +6683,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6708,22 +6708,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6733,22 +6733,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6758,22 +6758,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Stavudine (d4T), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV), Nelfinavir (NFV), Atazanavir (ATV), Lopinavir (LPV), Amprenavir (APV), Saquinavir (SQV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6783,7 +6783,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6808,7 +6808,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6833,7 +6833,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Stavudine (d4T), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV), Nelfinavir (NFV), Atazanavir (ATV), Lopinavir (LPV), Amprenavir (APV), Saquinavir (SQV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG)</t>
+          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6858,22 +6858,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6883,22 +6883,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6908,7 +6908,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37910452</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6933,22 +6933,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37910452</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6958,22 +6958,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT; Protease, PR</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -6983,22 +6983,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>37910452</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -7008,12 +7008,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>37910452</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -7033,12 +7033,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>RAL, EVG, DTG, BIC, CAB</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -7058,22 +7058,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -7083,22 +7083,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7108,12 +7108,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>RAL, EVG, DTG, BIC, CAB</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7158,22 +7158,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37941373</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7183,7 +7183,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NNRTI, PI, INSTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7208,22 +7208,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7233,22 +7233,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>37941373</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -7258,22 +7258,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7283,22 +7283,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37966701</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -7308,22 +7308,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37966701</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>cabotegravir, rilpivirine</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7333,22 +7333,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37973713</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -7358,22 +7358,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>37966701</t>
+          <t>37973713</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -7383,12 +7383,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>37966701</t>
+          <t>37973713</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>cabotegravir, rilpivirine</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -7413,17 +7413,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7433,7 +7433,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7458,7 +7458,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -7483,22 +7483,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7508,22 +7508,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -7533,22 +7533,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -7558,22 +7558,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37993493</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -7583,22 +7583,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37993493</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -7608,22 +7608,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -7633,22 +7633,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -7658,22 +7658,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7688,17 +7688,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7733,7 +7733,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7758,22 +7758,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38022124</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7783,12 +7783,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38022124</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7808,12 +7808,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38031075</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -7833,12 +7833,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>38022124</t>
+          <t>38031075</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Lamivudine, Tenofovir, Dolutegravir</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7858,12 +7858,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>38022124</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -7883,12 +7883,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>38031075</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2015-2019</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -7908,12 +7908,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>38031075</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Lamivudine, Tenofovir, Dolutegravir</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7958,22 +7958,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7983,22 +7983,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020, 2022, 2023</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -8008,12 +8008,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2015-2019</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -8033,22 +8033,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CSF, Plasma</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CSF</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -8058,22 +8058,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -8083,22 +8083,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -8108,22 +8108,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8133,22 +8133,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>38140649</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CSF, Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>CSF</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -8158,22 +8158,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140649</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -8183,22 +8183,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -8208,12 +8208,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -8233,12 +8233,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>38140649</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8258,12 +8258,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>38140649</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI; NRTI; NNRTI; PI</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>INSTI; NRTI; NNRTI; PI</t>
+          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8383,12 +8383,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8408,22 +8408,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -8433,22 +8433,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8458,22 +8458,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8533,22 +8533,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8558,22 +8558,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8583,22 +8583,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -8608,22 +8608,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8633,7 +8633,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -8683,22 +8683,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Gag, Pol, Env, Nef, vpu</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Envelope; Full genome; Near full length genome</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8708,7 +8708,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8733,22 +8733,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8758,22 +8758,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -8783,7 +8783,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
+          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8808,7 +8808,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8823,110 +8823,10 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
+          <t>Islatravir (ISL), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>38427738</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Gag, Pol, Env, Nef, vpu</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Envelope; Full genome; Near full length genome</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Islatravir (ISL), Lenacapavir (LEN)</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6463,17 +6463,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South America, Africa, USA</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6533,22 +6533,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37775947</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6563,17 +6563,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6608,22 +6608,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Envelope</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6658,22 +6658,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6708,22 +6708,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6733,22 +6733,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Stavudine (d4T), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV), Nelfinavir (NFV), Atazanavir (ATV), Lopinavir (LPV), Amprenavir (APV), Saquinavir (SQV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG)</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6783,22 +6783,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Stavudine (d4T), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV), Nelfinavir (NFV), Atazanavir (ATV), Lopinavir (LPV), Amprenavir (APV), Saquinavir (SQV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6858,22 +6858,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6888,17 +6888,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT; Protease, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6908,22 +6908,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>37910452</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6938,17 +6938,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6958,12 +6958,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37910452</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7008,12 +7008,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>RAL, EVG, DTG, BIC, CAB</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -7058,22 +7058,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RAL, EVG, DTG, BIC, CAB</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NNRTI, PI, INSTI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7158,22 +7158,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>37941373</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7183,22 +7183,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37941373</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7208,22 +7208,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7283,22 +7283,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>37966701</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>cabotegravir, rilpivirine</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7333,22 +7333,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37966701</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>cabotegravir, rilpivirine</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -7363,17 +7363,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -7388,17 +7388,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7433,12 +7433,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37973713</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -7483,22 +7483,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7513,17 +7513,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7558,22 +7558,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -7588,17 +7588,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -7608,22 +7608,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37993493</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7663,17 +7663,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7733,7 +7733,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7758,12 +7758,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>38022124</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7808,12 +7808,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>38031075</t>
+          <t>38022124</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Lamivudine, Tenofovir, Dolutegravir</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7858,12 +7858,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38031075</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Lamivudine, Tenofovir, Dolutegravir</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2015-2019</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>2015-2019</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7958,22 +7958,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -8013,17 +8013,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020, 2022, 2023</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -8033,22 +8033,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>CSF, Plasma</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>CSF</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -8058,22 +8058,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -8083,22 +8083,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>CSF, Plasma</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>CSF</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -8108,22 +8108,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8133,7 +8133,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>38140649</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -8158,7 +8158,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>38140649</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -8183,22 +8183,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38140649</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -8208,12 +8208,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38140649</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>INSTI; NRTI; NNRTI; PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8383,12 +8383,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>INSTI; NRTI; NNRTI; PI</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8408,12 +8408,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -8438,17 +8438,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8463,17 +8463,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8533,22 +8533,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8558,22 +8558,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8583,22 +8583,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -8683,22 +8683,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Nef, vpu</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Envelope; Full genome; Near full length genome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8708,7 +8708,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8738,17 +8738,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Gag, Pol, Env, Nef, vpu</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
+          <t>Envelope; Full genome; Near full length genome</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8758,12 +8758,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -8783,12 +8783,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
+          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8813,20 +8813,70 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
         <is>
           <t>Islatravir (ISL), Lenacapavir (LEN)</t>
         </is>
       </c>
-      <c r="E336" t="n">
+      <c r="E338" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,17 +688,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -938,17 +938,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -963,17 +963,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -988,17 +988,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
+          <t>Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NRTI, PI</t>
+          <t>AZT, 3TC, LPV</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AZT, 3TC, LPV</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Tenofovir alafenamide</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Tenofovir alafenamide</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Dolutegravir (DTG), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Efavirenz (EFV)</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI</t>
+          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2263,17 +2263,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2413,17 +2413,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2738,17 +2738,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RPV</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3263,17 +3263,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Lamivudine (3TC), Emtricitabine (FTC)</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Emtricitabine (FTC)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
+          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2014-2020</t>
+          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
+          <t>2014-2020</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Dolutegravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Bictegravir (BIC)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4588,17 +4588,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4613,17 +4613,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Lamivudine (3TC), Tenofovir (TFV), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Stavudine (D4T), Emtricitabine(FTC)</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Tenofovir (TFV), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Stavudine (D4T), Emtricitabine(FTC)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2016-2017, 2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>atazanavir, fosamprenavir, indinavir, saquinavir, nelfinavir, abacavir, didanosine, emtricitabine, lamivudine, azidothymidine, stavudine, tenofovir, doravirine, etravirine, nevirapine, rilpivirine, efavirenz, etravirine</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>atazanavir, fosamprenavir, indinavir, saquinavir, nelfinavir, abacavir, didanosine, emtricitabine, lamivudine, azidothymidine, stavudine, tenofovir, doravirine, etravirine, nevirapine, rilpivirine, efavirenz, etravirine</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>Lopinavir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Lopinavir, Dolutegravir, Raltegravir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>INSTI, NNRTI, PI, NRTI</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5538,17 +5538,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI, PI, NRTI</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5613,17 +5613,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5713,17 +5713,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INST</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5863,17 +5863,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>67939</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5963,17 +5963,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Protease, PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Darunavir, Lopinavir</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Darunavir, Lopinavir</t>
+          <t>Protease, PR</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6213,17 +6213,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TPV, D4T, AZT, ETR, RPV, NVP, EFV</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>TPV, D4T, AZT, ETR, RPV, NVP, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6363,17 +6363,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6463,17 +6463,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>South America, Africa, USA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6538,17 +6538,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
+          <t>South America, Africa, USA</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6563,17 +6563,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Envelope</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6863,17 +6863,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6908,22 +6908,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37910452</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT; Protease, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6938,17 +6938,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6958,12 +6958,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>37910452</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7008,12 +7008,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>RAL, EVG, DTG, BIC, CAB</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -7058,22 +7058,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>RAL, EVG, DTG, BIC, CAB</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7158,22 +7158,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37941373</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7183,22 +7183,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>37941373</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7208,22 +7208,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7283,22 +7283,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37966701</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>cabotegravir, rilpivirine</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7333,22 +7333,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>37966701</t>
+          <t>37973713</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>cabotegravir, rilpivirine</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -7363,17 +7363,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -7388,17 +7388,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -7413,17 +7413,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7433,12 +7433,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>37973713</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -7483,22 +7483,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7513,17 +7513,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7558,22 +7558,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37993493</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -7608,22 +7608,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -7638,17 +7638,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -7663,17 +7663,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7688,17 +7688,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7733,7 +7733,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7758,12 +7758,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38022124</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7808,12 +7808,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>38022124</t>
+          <t>38031075</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Dolutegravir (DTG), Elvitegravir (EVG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Lamivudine, Tenofovir, Dolutegravir</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7858,12 +7858,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>38031075</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Lamivudine, Tenofovir, Dolutegravir</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2015-2019</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>2015-2019</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7958,22 +7958,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -8058,7 +8058,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>CSF, Plasma</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>CSF</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -8083,22 +8083,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CSF, Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>CSF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -8108,22 +8108,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8158,12 +8158,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38140649</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -8208,12 +8208,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>38140649</t>
+          <t>38140667</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8263,17 +8263,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
+          <t>INSTI; NRTI; NNRTI; PI</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>INSTI; NRTI; NNRTI; PI</t>
+          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8408,22 +8408,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>38142692</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -8438,17 +8438,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8558,22 +8558,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>38142692</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8583,17 +8583,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -8688,17 +8688,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8708,7 +8708,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8738,17 +8738,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Nef, vpu</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Envelope; Full genome; Near full length genome</t>
+          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8763,17 +8763,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Gag, Pol, Env, Nef, vpu</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
+          <t>Envelope; Full genome; Near full length genome</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -8783,12 +8783,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>INSTI (Integrase Inhibitor), CAI (Capsid Inhibitor)</t>
+          <t>Islatravir (ISL), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -8858,25 +8858,2725 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>40391923</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Hair</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Islatravir (ISL), Lenacapavir (LEN)</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2006-2024</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>RT, PR, IN</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ATV/r, NFV, D4T, NVP, RAL</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Whole Blood</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Tenofovir (TFV), INSTIs, Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>40839365</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>TAF, FTC, TDF, 3TC, DTG, BIC</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>0 (Review paper)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>9685</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INST</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Illumina sequencing</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes  </t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>RT, IN, NC, Env</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Envelope; Integrase; Near full length genome</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>INSTI, PI, NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG), Darunavir (DRV), Tenofovir alafenamide (TAF), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Protease, PR; Gag</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>PBMC (Whole blood OK)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Whole Blood</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>INSTI, NRTI</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2015-2021</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Plasma (presumably)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Integrase, IN</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>TAF, FTC, LEN, BIC</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Emtricitabine/tenofovir alafenamide (F/TAF), TAF, bicegravir, LEN</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>USA, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Sanger (not stated)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Plasma (not stated)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>AZT, D4T, TDF, ABC</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>INSTI, NRTI</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Near full length genome</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>No (Published sequences only)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> None</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, FNC, ABC, FTC, NVP, ETR, EFV</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>8654, 10551</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>China, United States</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>1978-2023</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Zidovudine (AZT), Stavudine (D4T), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Yes (PrEP)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2015-2025</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
         <v>0</v>
       </c>
     </row>
